--- a/src/main/resources/espacios/Software/PENDIENTE_Azure.xlsx
+++ b/src/main/resources/espacios/Software/PENDIENTE_Azure.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -38,6 +38,7 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -97,8 +98,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -247,7 +252,7 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>0</v>
       </c>
     </row>
